--- a/vrn_processing/vehicle_check_results_with_weights.xlsx
+++ b/vrn_processing/vehicle_check_results_with_weights.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,19 +443,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CG04HW4617</t>
+          <t>PR1KHA0037</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42000</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CG13QO920</t>
+          <t>MAT4401866</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -467,300 +467,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CG10EF8100</t>
+          <t>JK22DD5057</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CG04JD6073</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>35000</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CG04LQ0387</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>42000</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>OD04R3798</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>42000</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CG10CD7257</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7200</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CG1OBL4140</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CG10BL1207</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CG10AP6011</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CG10CC4357</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CG10BL6477</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CG10R2013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MH4OAK4226</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CG10CC4157</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>JH05A0327</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CG08AD3601</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CG08AA7581</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2980</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CG10BX9767</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CG10CD4457</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>OD05AX0560</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>CG10AH2375</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2510</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>CG04QW8016</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>18500</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>CG13BK7586</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>18500</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CG1OAV7862</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TN31CH9732</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>CG10BM7246</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7200</t>
         </is>
       </c>
     </row>
